--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,61 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>16809547</v>
+        <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>43378</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>201075</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Boloria selene</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Florarna, 2 km N Risön, Upl</t>
+          <t>Täften, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658472</v>
+        <v>658490</v>
       </c>
       <c r="R2" t="n">
-        <v>6690847</v>
+        <v>6690931</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-06-21</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,24 +765,758 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Michael Taylor</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Michael Taylor</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137370823</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>16809547</v>
+      </c>
+      <c r="B3" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Florarna, 2 km N Risön, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>658472</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6690847</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2013-06-21</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2013-06-21</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Michael Taylor</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Michael Taylor</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/16809547</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>137370633</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99388</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Täften, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>658441</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6690938</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370633</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137370618</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102541</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Täften, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>658446</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6690929</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370618</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137370625</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102541</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Täften, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>658447</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6690928</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370625</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137370842</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102541</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Täften, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>658488</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6690930</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370842</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137370519</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101625</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Täften, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>658444</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6690897</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370519</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137370931</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101625</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Täften, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>658487</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6690928</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Österlövsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137370931</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137370633</v>
       </c>
       <c r="B4" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137370618</v>
       </c>
       <c r="B5" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>137370625</v>
       </c>
       <c r="B6" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>137370842</v>
       </c>
       <c r="B7" t="n">
-        <v>102541</v>
+        <v>102544</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137370519</v>
       </c>
       <c r="B8" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>137370931</v>
       </c>
       <c r="B9" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137370633</v>
       </c>
       <c r="B4" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137370618</v>
       </c>
       <c r="B5" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>137370625</v>
       </c>
       <c r="B6" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>137370842</v>
       </c>
       <c r="B7" t="n">
-        <v>102544</v>
+        <v>102550</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137370519</v>
       </c>
       <c r="B8" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>137370931</v>
       </c>
       <c r="B9" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137370633</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137370618</v>
       </c>
       <c r="B5" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>137370625</v>
       </c>
       <c r="B6" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>137370842</v>
       </c>
       <c r="B7" t="n">
-        <v>102550</v>
+        <v>102562</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137370519</v>
       </c>
       <c r="B8" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>137370931</v>
       </c>
       <c r="B9" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137370633</v>
       </c>
       <c r="B4" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137370618</v>
       </c>
       <c r="B5" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>137370625</v>
       </c>
       <c r="B6" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>137370842</v>
       </c>
       <c r="B7" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137370519</v>
       </c>
       <c r="B8" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>137370931</v>
       </c>
       <c r="B9" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137370633</v>
       </c>
       <c r="B4" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137370618</v>
       </c>
       <c r="B5" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>137370625</v>
       </c>
       <c r="B6" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>137370842</v>
       </c>
       <c r="B7" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137370519</v>
       </c>
       <c r="B8" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>137370931</v>
       </c>
       <c r="B9" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 63261-2025 artfynd.xlsx
+++ b/artfynd/A 63261-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137370823</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>137370633</v>
       </c>
       <c r="B4" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1002,7 +1002,7 @@
         <v>137370618</v>
       </c>
       <c r="B5" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>137370625</v>
       </c>
       <c r="B6" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
         <v>137370842</v>
       </c>
       <c r="B7" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>137370519</v>
       </c>
       <c r="B8" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>137370931</v>
       </c>
       <c r="B9" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
